--- a/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_CAQ.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_CAQ.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Thiam (15 L)</t>
+          <t>A. Thiam (26 L)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Thiam (12.0 3PA)</t>
+          <t>A. Thiam (18.0 3PA)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Shoats (2.0)</t>
+          <t>J. Shoats (1.714)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Restricted Area (27 L)</t>
+          <t>Above the Break 3 (40 L)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Restricted Area (59.3%)</t>
+          <t>Restricted Area (62.5%)</t>
         </is>
       </c>
     </row>
@@ -545,15 +545,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -574,7 +574,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -592,7 +592,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -944,107 +944,107 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.192307692307692</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
         <v>12</v>
       </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.133333333333333</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -1072,43 +1072,43 @@
         </is>
       </c>
       <c r="AQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
         <v>3</v>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>2</v>
-      </c>
       <c r="AY2" t="n">
         <v>1</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BC2" t="n">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1136,11 +1136,11 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -1176,53 +1176,53 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>17</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>13</v>
       </c>
-      <c r="H3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>10</v>
-      </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -1242,15 +1242,15 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1279,12 +1279,32 @@
           <t>66.7%</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr">
         <is>
           <t>Restricted Area</t>
@@ -1300,15 +1320,15 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1317,11 +1337,11 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AV3" t="n">
@@ -1329,18 +1349,18 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
@@ -1348,14 +1368,14 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1364,15 +1384,15 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -1394,42 +1414,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322040</t>
+          <t>322041</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1445,16 +1465,16 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -1465,55 +1485,65 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>4</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
@@ -1523,37 +1553,37 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AT4" t="n">
         <v>4</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
@@ -1561,14 +1591,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -1580,27 +1610,27 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
         <v>5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>3</v>
-      </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1626,21 +1656,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CAQ_J._SHOATS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>322041</t>
+          <t>322040</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
         <v>10</v>
@@ -1650,191 +1680,685 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
         <v>6</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="AK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
         <v>3</v>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
         <v>4</v>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>1</v>
       </c>
       <c r="AY5" t="n">
         <v>4</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
         <v>4</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>248528</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>7</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>274423</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="AX7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="BG5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH5" t="inlineStr">
+      <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -1851,15 +2375,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -1880,7 +2404,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -1898,7 +2422,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -2250,53 +2774,53 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -2307,7 +2831,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -2316,46 +2840,56 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
@@ -2365,7 +2899,7 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -2374,79 +2908,79 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
         <v>3</v>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AV2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="BA2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH2" t="inlineStr">
         <is>
           <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2468,209 +3002,219 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAQ_A._THIAM</t>
+          <t>CAQ_I._PAVICEVIC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>322038</t>
+          <t>274423</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A. Thiam</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
         <v>15</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="I3" t="n">
-        <v>17</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
         <v>5</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>1.133333333333333</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V3" t="n">
-        <v>9</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AN3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
         <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
@@ -2678,7 +3222,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2700,49 +3244,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_A._THIAM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322040</t>
+          <t>322038</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>A. Thiam</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -2751,36 +3295,36 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.192307692307692</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -2788,33 +3332,33 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -2825,20 +3369,20 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AQ4" t="n">
@@ -2846,7 +3390,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2855,26 +3399,26 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -2882,7 +3426,7 @@
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -2890,19 +3434,19 @@
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
@@ -2932,174 +3476,194 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>322042</t>
+          <t>322040</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>22</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
         <v>6</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>76.9%</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AV5" t="n">
-        <v>2</v>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
@@ -3114,7 +3678,7 @@
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -3122,19 +3686,19 @@
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
         <v>4</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
@@ -3143,6 +3707,490 @@
       <c r="BH5" t="inlineStr">
         <is>
           <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>322042</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>17</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>13</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>248528</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -3157,15 +4205,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -3186,7 +4234,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -3204,7 +4252,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -3556,107 +4604,107 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.192307692307692</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
         <v>12</v>
       </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.133333333333333</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -3671,11 +4719,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -3684,43 +4732,43 @@
         </is>
       </c>
       <c r="AQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
         <v>3</v>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>2</v>
-      </c>
       <c r="AY2" t="n">
         <v>1</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -3728,7 +4776,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BC2" t="n">
@@ -3739,7 +4787,7 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -3748,11 +4796,11 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -3774,67 +4822,67 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>322040</t>
+          <t>322042</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -3849,7 +4897,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -3858,11 +4906,11 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3871,11 +4919,11 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3888,15 +4936,35 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr">
         <is>
           <t>Restricted Area</t>
@@ -3907,7 +4975,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -3916,11 +4984,11 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -3929,62 +4997,62 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>500.0%</t>
         </is>
       </c>
-      <c r="BC3" t="n">
+      <c r="BG3" t="n">
         <v>5</v>
       </c>
-      <c r="BD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BG3" t="n">
-        <v>3</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -4006,95 +5074,95 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAQ_J._SHOATS</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322041</t>
+          <t>248528</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4107,20 +5175,20 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -4131,28 +5199,28 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -4165,58 +5233,58 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -4238,174 +5306,194 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>322042</t>
+          <t>322040</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>22</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
         <v>6</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>76.9%</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AV5" t="n">
-        <v>2</v>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
@@ -4420,7 +5508,7 @@
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -4428,19 +5516,19 @@
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
         <v>4</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
@@ -4449,6 +5537,490 @@
       <c r="BH5" t="inlineStr">
         <is>
           <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CAQ_J._SHOATS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>322041</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>J. Shoats</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I6" t="n">
+        <v>36</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>81.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>88.2%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>81.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>7</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>274423</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4492,7 +6064,7 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -4510,7 +6082,7 @@
     <col width="16" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -4862,107 +6434,107 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.192307692307692</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
         <v>12</v>
       </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.133333333333333</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -4977,11 +6549,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -4990,43 +6562,43 @@
         </is>
       </c>
       <c r="AQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
         <v>3</v>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>2</v>
-      </c>
       <c r="AY2" t="n">
         <v>1</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -5034,7 +6606,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BC2" t="n">
@@ -5045,7 +6617,7 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -5054,11 +6626,11 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -5073,7 +6645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5224,41 +6796,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.185185185185185</v>
+        <v>0.975</v>
       </c>
       <c r="J2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -5269,7 +6841,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -5277,7 +6849,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -5285,7 +6857,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -5307,41 +6879,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.153846153846154</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="J3" t="n">
+        <v>38</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>26</v>
-      </c>
-      <c r="M3" t="n">
-        <v>10</v>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -5360,7 +6932,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -5390,31 +6962,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8888888888888888</v>
+        <v>1.25</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -5424,18 +6996,18 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -5443,11 +7015,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5471,27 +7049,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -5501,18 +7079,18 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -5520,11 +7098,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5548,7 +7132,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -5558,11 +7142,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -5571,37 +7155,114 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5614,7 +7275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5769,27 +7430,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J2" t="n">
         <v>32</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>59.3%</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>1.185185185185185</v>
-      </c>
-      <c r="J2" t="n">
-        <v>27</v>
-      </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -5799,14 +7460,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -5814,7 +7475,7 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -5822,7 +7483,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -5848,41 +7509,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.153846153846154</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="J3" t="n">
+        <v>38</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>26</v>
-      </c>
-      <c r="M3" t="n">
-        <v>10</v>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -5901,7 +7562,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -5910,6 +7571,172 @@
       <c r="U3" t="inlineStr">
         <is>
           <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>32.5%</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>40</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>30.3%</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -5924,15 +7751,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -6112,21 +7939,21 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -6135,14 +7962,14 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -6161,7 +7988,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -6210,13 +8037,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -6227,10 +8054,10 @@
         <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -6240,7 +8067,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -6289,46 +8116,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322042</t>
+          <t>322040</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
         <v>6</v>
       </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.333333333333333</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" t="n">
         <v>6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -6338,7 +8165,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -6387,46 +8214,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>322040</t>
+          <t>322041</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="M5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" t="n">
         <v>6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -6436,7 +8263,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -6447,7 +8274,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -6455,7 +8282,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -6463,7 +8290,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -6485,83 +8312,769 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>322040</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>CAQ_D._HORTA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>248528</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>D. Horta</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>322042</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>322040</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>322042</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>274423</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>274423</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>5</v>
       </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Queluz O NOSSO PREGO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CAQ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>322042</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -6590,7 +9103,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -6764,21 +9277,21 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -6787,14 +9300,14 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -6813,7 +9326,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W2" t="n">
